--- a/data/trans_orig/IP3106-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP3106-Edad-trans_orig.xlsx
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3271</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2629</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>2651</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10409</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>2219</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10182</t>
+          <t>9335</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6287</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16557</t>
+          <t>16444</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6642</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15938</t>
+          <t>16137</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9650</t>
+          <t>9797</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20116</t>
+          <t>20505</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17946</t>
+          <t>18874</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32603</t>
+          <t>32552</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41908</t>
+          <t>42093</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53391</t>
+          <t>53442</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>49616</t>
+          <t>48950</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>61667</t>
+          <t>61357</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>95569</t>
+          <t>95916</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>112627</t>
+          <t>112759</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>80,05%</t>
         </is>
       </c>
     </row>
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>670</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5730</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>667</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>5553</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3964</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>3541</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8700</t>
+          <t>8734</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20697</t>
+          <t>20595</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9915</t>
+          <t>9119</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22447</t>
+          <t>22060</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20980</t>
+          <t>20739</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39223</t>
+          <t>37822</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39389</t>
+          <t>39253</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>60683</t>
+          <t>60489</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>40504</t>
+          <t>39625</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>59614</t>
+          <t>59896</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2030,12 +2030,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>84389</t>
+          <t>85491</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>112425</t>
+          <t>113128</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,4%</t>
         </is>
       </c>
     </row>
@@ -2093,12 +2093,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>175357</t>
+          <t>174878</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>198768</t>
+          <t>199273</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>175696</t>
+          <t>176004</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>198203</t>
+          <t>198160</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>358950</t>
+          <t>357591</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>390968</t>
+          <t>389966</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,22%</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>3237</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>2720</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2662,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5959</t>
+          <t>5408</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15917</t>
+          <t>15742</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2818</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10583</t>
+          <t>10897</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>10575</t>
+          <t>10414</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>23265</t>
+          <t>23509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12841</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25963</t>
+          <t>25364</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15601</t>
+          <t>15784</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29529</t>
+          <t>29258</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31287</t>
+          <t>31491</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51271</t>
+          <t>50036</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2888,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>89518</t>
+          <t>89508</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>104382</t>
+          <t>104395</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>103620</t>
+          <t>103794</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>119453</t>
+          <t>118493</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>198253</t>
+          <t>198259</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>220550</t>
+          <t>219522</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,43%</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3590</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7977</t>
+          <t>7965</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>4685</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13478</t>
+          <t>13327</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7146</t>
+          <t>7248</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>19070</t>
+          <t>18366</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>25251</t>
+          <t>25810</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>42230</t>
+          <t>43394</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>27352</t>
+          <t>28534</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>45538</t>
+          <t>45122</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>58545</t>
+          <t>56930</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>81412</t>
+          <t>82000</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3655,12 +3655,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,63%</t>
         </is>
       </c>
     </row>
@@ -3683,12 +3683,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>145949</t>
+          <t>145009</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>163496</t>
+          <t>163185</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>150940</t>
+          <t>151045</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>170082</t>
+          <t>168553</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,12 +3753,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>302592</t>
+          <t>301751</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>327902</t>
+          <t>328830</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,72%</t>
         </is>
       </c>
     </row>
@@ -4061,12 +4061,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>671</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>6532</t>
+          <t>6254</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4076,12 +4076,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>669</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>6254</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -4252,12 +4252,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>24700</t>
+          <t>24719</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>42623</t>
+          <t>43801</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>24999</t>
+          <t>24627</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>44372</t>
+          <t>42788</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4302,12 +4302,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>55178</t>
+          <t>54611</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>82079</t>
+          <t>80981</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4337,12 +4337,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -4365,12 +4365,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>96917</t>
+          <t>97225</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>127736</t>
+          <t>126981</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4380,12 +4380,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>105912</t>
+          <t>105849</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>136995</t>
+          <t>137523</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>212908</t>
+          <t>212776</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>257466</t>
+          <t>258197</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,71%</t>
         </is>
       </c>
     </row>
@@ -4478,12 +4478,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>471486</t>
+          <t>471538</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>504997</t>
+          <t>503844</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4493,12 +4493,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>497848</t>
+          <t>499662</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>532869</t>
+          <t>533140</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,12 +4548,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>979215</t>
+          <t>979893</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1030657</t>
+          <t>1027893</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,48%</t>
         </is>
       </c>
     </row>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3394</t>
+          <t>3610</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3143</t>
+          <t>3760</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5629</t>
+          <t>5477</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5198</t>
+          <t>5982</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>925</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8436</t>
+          <t>8087</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -5392,12 +5392,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7428</t>
+          <t>6832</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5407,12 +5407,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10044</t>
+          <t>9869</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>4743</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14770</t>
+          <t>14632</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82362</t>
+          <t>82526</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>89830</t>
+          <t>89861</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5520,82 +5520,82 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>89,81%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>97,8%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>80192</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>74823</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>84146</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>91,4%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>85,28%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>95,91%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>167130</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>161000</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>172368</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>93,04%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>89,63%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>97,76%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>80192</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>74634</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>84064</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>91,4%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>85,07%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>95,81%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>167130</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>159029</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>171762</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>93,04%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>88,53%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>2786</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4498</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4816</t>
+          <t>5497</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -6074,12 +6074,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>5435</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17176</t>
+          <t>16257</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6089,12 +6089,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6109,12 +6109,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2149</t>
+          <t>2271</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10020</t>
+          <t>10771</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6124,12 +6124,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6144,12 +6144,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9097</t>
+          <t>10228</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22344</t>
+          <t>23452</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6159,12 +6159,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9410</t>
+          <t>8867</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21046</t>
+          <t>20963</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6202,12 +6202,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16631</t>
+          <t>16686</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33213</t>
+          <t>33284</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>29752</t>
+          <t>29622</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>49135</t>
+          <t>51358</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -6300,12 +6300,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>202201</t>
+          <t>201887</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>217946</t>
+          <t>217873</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>227124</t>
+          <t>227902</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>245240</t>
+          <t>245372</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>435523</t>
+          <t>434577</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>459632</t>
+          <t>458759</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,13%</t>
         </is>
       </c>
     </row>
@@ -6761,7 +6761,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4246</t>
+          <t>3688</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5748</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>6538</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -6869,12 +6869,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7583</t>
+          <t>7039</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6904,12 +6904,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>4312</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14128</t>
+          <t>14314</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6919,12 +6919,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6939,12 +6939,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6869</t>
+          <t>6986</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>18409</t>
+          <t>19572</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -6982,12 +6982,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14870</t>
+          <t>15321</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7017,12 +7017,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5539</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15473</t>
+          <t>14392</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7052,12 +7052,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12831</t>
+          <t>12174</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27381</t>
+          <t>26018</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -7095,12 +7095,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>135371</t>
+          <t>134510</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>147054</t>
+          <t>146791</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7110,12 +7110,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7130,12 +7130,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>129811</t>
+          <t>130901</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>144280</t>
+          <t>143876</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7145,12 +7145,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7165,12 +7165,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>269615</t>
+          <t>270125</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>287713</t>
+          <t>288994</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,5%</t>
         </is>
       </c>
     </row>
@@ -7664,12 +7664,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1414</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7798</t>
+          <t>7640</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7679,12 +7679,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7699,12 +7699,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>859</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7234</t>
+          <t>6657</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7714,12 +7714,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2798</t>
+          <t>2971</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10885</t>
+          <t>10921</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7749,12 +7749,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -7777,12 +7777,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4735</t>
+          <t>5192</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15263</t>
+          <t>15737</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7812,12 +7812,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4198</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>13197</t>
+          <t>13067</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7827,12 +7827,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>11358</t>
+          <t>11578</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>24990</t>
+          <t>25361</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7862,12 +7862,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -7890,12 +7890,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>152040</t>
+          <t>151682</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>163445</t>
+          <t>163352</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7925,12 +7925,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>161249</t>
+          <t>161202</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>171745</t>
+          <t>171291</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7940,12 +7940,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7960,12 +7960,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>317551</t>
+          <t>316839</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>333341</t>
+          <t>332457</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7975,12 +7975,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3360</t>
+          <t>3829</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8323,7 +8323,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -8351,7 +8351,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>4499</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8381,12 +8381,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7189</t>
+          <t>6693</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8396,12 +8396,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8416,12 +8416,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>1422</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>8273</t>
+          <t>8446</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -8459,12 +8459,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>12123</t>
+          <t>11909</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26939</t>
+          <t>26770</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8474,12 +8474,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8494,12 +8494,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>11831</t>
+          <t>11664</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>26107</t>
+          <t>27221</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8509,12 +8509,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8529,12 +8529,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>26939</t>
+          <t>27401</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>48615</t>
+          <t>47944</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8544,12 +8544,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -8572,12 +8572,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>26619</t>
+          <t>25961</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>45231</t>
+          <t>44887</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8587,12 +8587,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8607,12 +8607,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>36811</t>
+          <t>37679</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>60017</t>
+          <t>59484</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8622,12 +8622,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8642,12 +8642,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>69091</t>
+          <t>68323</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>96673</t>
+          <t>97743</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8657,12 +8657,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -8685,12 +8685,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>586091</t>
+          <t>587242</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>609739</t>
+          <t>611351</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8720,12 +8720,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>607228</t>
+          <t>607965</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>634470</t>
+          <t>634885</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1203301</t>
+          <t>1202947</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1237696</t>
+          <t>1237592</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2708</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -9486,12 +9486,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>727</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>7147</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7674</t>
+          <t>7531</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -9599,12 +9599,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4653</t>
+          <t>4377</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12729</t>
+          <t>12677</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9614,12 +9614,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6615</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16648</t>
+          <t>16437</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12034</t>
+          <t>12835</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25102</t>
+          <t>25939</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -9712,12 +9712,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69169</t>
+          <t>69694</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>79102</t>
+          <t>78785</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9727,12 +9727,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9747,12 +9747,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62503</t>
+          <t>62887</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72888</t>
+          <t>73443</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9762,12 +9762,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9782,12 +9782,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>136423</t>
+          <t>136165</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>150537</t>
+          <t>149716</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9797,12 +9797,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,22%</t>
         </is>
       </c>
     </row>
@@ -10208,7 +10208,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4735</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5192</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -10281,12 +10281,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6412</t>
+          <t>6432</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10296,12 +10296,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10316,12 +10316,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5282</t>
+          <t>5471</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15724</t>
+          <t>16271</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10331,12 +10331,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10351,12 +10351,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7437</t>
+          <t>7463</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19382</t>
+          <t>19151</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10371,7 +10371,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -10394,12 +10394,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15300</t>
+          <t>15059</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29573</t>
+          <t>28715</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10409,12 +10409,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10429,12 +10429,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14595</t>
+          <t>14822</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29678</t>
+          <t>28893</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10444,12 +10444,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10464,12 +10464,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>33498</t>
+          <t>32334</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>54052</t>
+          <t>52364</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10479,12 +10479,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -10507,12 +10507,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>174655</t>
+          <t>174757</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>190008</t>
+          <t>189678</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10522,12 +10522,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10542,12 +10542,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>217323</t>
+          <t>216661</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>235113</t>
+          <t>234629</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10557,12 +10557,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10577,12 +10577,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>396634</t>
+          <t>398705</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>419990</t>
+          <t>421724</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10592,12 +10592,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,56%</t>
         </is>
       </c>
     </row>
@@ -10968,7 +10968,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>4562</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11038,7 +11038,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2975</t>
+          <t>3175</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11623</t>
+          <t>11426</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11091,12 +11091,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11111,12 +11111,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1641</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10295</t>
+          <t>9674</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11126,12 +11126,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11146,12 +11146,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6280</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17396</t>
+          <t>18013</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11161,12 +11161,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -11189,12 +11189,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15675</t>
+          <t>15583</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30339</t>
+          <t>30318</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15081</t>
+          <t>14617</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30376</t>
+          <t>28866</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11239,12 +11239,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11259,12 +11259,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33823</t>
+          <t>33444</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>54216</t>
+          <t>54334</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11274,12 +11274,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -11302,12 +11302,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>146689</t>
+          <t>147321</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>163564</t>
+          <t>164273</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11317,12 +11317,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11337,12 +11337,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>153402</t>
+          <t>154566</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>169744</t>
+          <t>169987</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11352,12 +11352,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11372,12 +11372,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>307105</t>
+          <t>307503</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>330943</t>
+          <t>329658</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11387,12 +11387,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,15%</t>
         </is>
       </c>
     </row>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>4643</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>5076</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -11871,12 +11871,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2497</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9922</t>
+          <t>10122</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11886,12 +11886,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11906,12 +11906,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4291</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13457</t>
+          <t>14028</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11921,12 +11921,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11941,12 +11941,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8426</t>
+          <t>7817</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>20153</t>
+          <t>19816</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11956,12 +11956,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -11984,12 +11984,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13329</t>
+          <t>12397</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>27520</t>
+          <t>26511</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11999,12 +11999,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12019,12 +12019,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9435</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>21914</t>
+          <t>22221</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12034,12 +12034,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12054,12 +12054,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>25769</t>
+          <t>26309</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>45429</t>
+          <t>45406</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12069,12 +12069,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -12097,12 +12097,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>138959</t>
+          <t>139471</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>154510</t>
+          <t>154921</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12112,12 +12112,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>136372</t>
+          <t>136770</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>151423</t>
+          <t>151933</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12167,12 +12167,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>280406</t>
+          <t>279592</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>303093</t>
+          <t>302253</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,42%</t>
         </is>
       </c>
     </row>
@@ -12558,7 +12558,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4831</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12588,12 +12588,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12628,7 +12628,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>8056</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12643,7 +12643,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -12666,12 +12666,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>11853</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>24808</t>
+          <t>24576</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12681,12 +12681,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12701,12 +12701,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>16013</t>
+          <t>15953</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>32355</t>
+          <t>31679</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12716,12 +12716,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12736,12 +12736,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>30181</t>
+          <t>31093</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>52449</t>
+          <t>52231</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12751,12 +12751,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -12779,12 +12779,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>60034</t>
+          <t>59004</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>84867</t>
+          <t>84980</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12794,12 +12794,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12814,12 +12814,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>56995</t>
+          <t>56309</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>82864</t>
+          <t>83322</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12849,12 +12849,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>121661</t>
+          <t>121350</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>158124</t>
+          <t>158034</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -12892,12 +12892,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>547148</t>
+          <t>547300</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>575405</t>
+          <t>576086</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12907,12 +12907,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12927,12 +12927,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>588596</t>
+          <t>587283</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>618102</t>
+          <t>616983</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12962,12 +12962,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1143914</t>
+          <t>1143461</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1184135</t>
+          <t>1185296</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,97%</t>
         </is>
       </c>
     </row>
@@ -13693,12 +13693,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>454</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4274</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13708,12 +13708,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13728,12 +13728,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>715</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4119</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -13743,12 +13743,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13763,12 +13763,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6820</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13778,12 +13778,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8079</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17150</t>
+          <t>17262</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -13821,12 +13821,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -13841,12 +13841,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5709</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13703</t>
+          <t>13954</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -13856,12 +13856,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -13876,12 +13876,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15817</t>
+          <t>15617</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>27774</t>
+          <t>28318</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -13891,12 +13891,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,86%</t>
         </is>
       </c>
     </row>
@@ -13919,12 +13919,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27590</t>
+          <t>27112</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36566</t>
+          <t>36852</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -13934,12 +13934,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -13954,12 +13954,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29295</t>
+          <t>29139</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38137</t>
+          <t>37958</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -13989,12 +13989,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>60045</t>
+          <t>59126</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>72702</t>
+          <t>72444</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14004,12 +14004,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>78,93%</t>
         </is>
       </c>
     </row>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14204,7 +14204,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14239,7 +14239,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -14375,12 +14375,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>519</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4678</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14390,12 +14390,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14445,12 +14445,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>514</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>4786</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14465,7 +14465,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -14488,12 +14488,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6529</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16251</t>
+          <t>16259</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14503,12 +14503,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14523,12 +14523,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10399</t>
+          <t>10349</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24107</t>
+          <t>24586</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14538,47 +14538,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>5,69%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>13,51%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>27050</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>19528</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>36117</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>7,93%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>5,72%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>13,25%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>27050</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>20012</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>37554</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>5,86%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -14601,12 +14601,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26296</t>
+          <t>25414</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>43341</t>
+          <t>42817</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -14616,12 +14616,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -14636,12 +14636,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>35212</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>54451</t>
+          <t>54381</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -14651,12 +14651,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -14671,12 +14671,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>65151</t>
+          <t>63957</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>91484</t>
+          <t>90586</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -14686,12 +14686,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,54%</t>
         </is>
       </c>
     </row>
@@ -14714,12 +14714,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>102938</t>
+          <t>103044</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>121618</t>
+          <t>121951</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14729,12 +14729,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14749,12 +14749,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>110144</t>
+          <t>109604</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>131514</t>
+          <t>130792</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14764,12 +14764,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>220094</t>
+          <t>220223</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>249026</t>
+          <t>248618</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14799,12 +14799,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,85%</t>
         </is>
       </c>
     </row>
@@ -15170,12 +15170,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>379</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>4981</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15190,7 +15190,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15210,7 +15210,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>4441</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15225,7 +15225,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15245,7 +15245,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6427</t>
+          <t>6796</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -15283,12 +15283,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9752</t>
+          <t>10145</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15298,12 +15298,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15318,12 +15318,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12411</t>
+          <t>12896</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29006</t>
+          <t>29327</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15333,12 +15333,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15353,12 +15353,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>17105</t>
+          <t>17050</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>34614</t>
+          <t>34723</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15368,12 +15368,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -15396,12 +15396,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34842</t>
+          <t>34232</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57124</t>
+          <t>57416</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15411,12 +15411,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15431,12 +15431,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32177</t>
+          <t>32679</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53869</t>
+          <t>55622</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15446,12 +15446,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15466,12 +15466,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>73289</t>
+          <t>72776</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>105163</t>
+          <t>104152</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15481,12 +15481,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,05%</t>
         </is>
       </c>
     </row>
@@ -15509,12 +15509,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>109042</t>
+          <t>109100</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>131743</t>
+          <t>132838</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15524,12 +15524,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15544,12 +15544,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>138049</t>
+          <t>133451</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>162343</t>
+          <t>161023</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15559,12 +15559,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15579,12 +15579,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>252812</t>
+          <t>253790</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>287440</t>
+          <t>286558</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15594,12 +15594,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,43%</t>
         </is>
       </c>
     </row>
@@ -15970,7 +15970,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -15985,7 +15985,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -16000,12 +16000,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>11829</t>
+          <t>11317</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -16020,7 +16020,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -16035,12 +16035,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>12486</t>
+          <t>12558</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -16050,12 +16050,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -16078,12 +16078,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>7187</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>19891</t>
+          <t>19044</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16093,12 +16093,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16113,12 +16113,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>11956</t>
+          <t>12193</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>28518</t>
+          <t>27648</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16128,12 +16128,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16148,12 +16148,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>22796</t>
+          <t>22339</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>43412</t>
+          <t>41887</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16163,12 +16163,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -16191,12 +16191,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>50905</t>
+          <t>49783</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>143747</t>
+          <t>130299</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16206,12 +16206,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16226,12 +16226,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>55983</t>
+          <t>55416</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>90643</t>
+          <t>90146</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16241,12 +16241,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16261,12 +16261,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>115770</t>
+          <t>114788</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>216304</t>
+          <t>211569</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16276,12 +16276,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>36,52%</t>
         </is>
       </c>
     </row>
@@ -16304,12 +16304,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>121943</t>
+          <t>133730</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>208504</t>
+          <t>209616</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16319,12 +16319,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16339,12 +16339,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>192209</t>
+          <t>189965</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>228531</t>
+          <t>228847</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16354,12 +16354,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16374,12 +16374,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>334821</t>
+          <t>332019</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>425974</t>
+          <t>427398</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16389,12 +16389,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>73,78%</t>
         </is>
       </c>
     </row>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>3051</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16589,7 +16589,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16609,7 +16609,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3039</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -16624,7 +16624,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
     </row>
@@ -16760,12 +16760,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>8431</t>
+          <t>8442</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -16795,12 +16795,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1558</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>12894</t>
+          <t>12506</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16810,12 +16810,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16830,12 +16830,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5135</t>
+          <t>5232</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>17536</t>
+          <t>16828</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16850,7 +16850,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -16873,12 +16873,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>21786</t>
+          <t>22247</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>39865</t>
+          <t>39751</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -16888,12 +16888,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -16908,12 +16908,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>44196</t>
+          <t>45121</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>71293</t>
+          <t>70735</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -16923,12 +16923,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -16943,12 +16943,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>71179</t>
+          <t>70615</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>103903</t>
+          <t>102454</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -16958,12 +16958,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -16986,12 +16986,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>139015</t>
+          <t>136470</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>246316</t>
+          <t>236877</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17001,12 +17001,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17021,12 +17021,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>147044</t>
+          <t>143449</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>192030</t>
+          <t>189261</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17036,12 +17036,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17056,12 +17056,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>297802</t>
+          <t>296794</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>415203</t>
+          <t>400601</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17071,12 +17071,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>28,67%</t>
         </is>
       </c>
     </row>
@@ -17099,12 +17099,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>386255</t>
+          <t>389174</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>479913</t>
+          <t>481303</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17134,12 +17134,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>491430</t>
+          <t>490860</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>538922</t>
+          <t>540340</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17149,12 +17149,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17169,12 +17169,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>898558</t>
+          <t>903231</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1004536</t>
+          <t>1004248</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17184,12 +17184,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,87%</t>
         </is>
       </c>
     </row>
